--- a/finance/output/SP500_Financial_Metrics_20250429_111632.xlsx
+++ b/finance/output/SP500_Financial_Metrics_20250429_111632.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\finance_script\finance\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3623BAD-161B-4FA7-A906-C63C4513502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA15DD6-0B69-486F-8056-427DB7ED8EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8794,6 +8794,9 @@
   <dimension ref="A1:H504"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="23.9296875" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.46484375" customWidth="1"/>
     <col min="7" max="7" width="16.1328125" customWidth="1"/>
     <col min="8" max="8" width="24.19921875" customWidth="1"/>
   </cols>
